--- a/23_Fintech_Payments/_template_FINTECH.xlsx
+++ b/23_Fintech_Payments/_template_FINTECH.xlsx
@@ -372,88 +372,92 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -712,54 +716,54 @@
   <dimension ref="B2:C8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -782,140 +786,140 @@
   <dimension ref="B2:D20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>0.025</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <v>0.015</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="8" t="n">
         <v>0.6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="8" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="10" t="n">
         <f aca="false">C5*C6</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="10" t="n">
         <f aca="false">C5*C7</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="11" t="n">
         <f aca="false">C14-C15</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="12" t="n">
         <f aca="false">IFERROR(1/C11,"-")</f>
         <v>33.3333333333333</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C18" s="11" t="n">
         <f aca="false">C9*C10*C17</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="12" t="str">
+      <c r="C19" s="13" t="str">
         <f aca="false">IFERROR(C18/C8,"-")</f>
         <v>-</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="14" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="11" t="str">
+      <c r="C20" s="12" t="str">
         <f aca="false">IFERROR(C8/(C9*C10),"-")</f>
         <v>-</v>
       </c>
@@ -939,214 +943,214 @@
   <dimension ref="B2:J12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="9" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="14" t="n">
+      <c r="D5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="14" t="n">
+      <c r="D6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="14" t="n">
+      <c r="D7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="14" t="n">
+      <c r="D8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <f aca="false">AVERAGE(C5:C8)</f>
         <v>1</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="16" t="n">
         <f aca="false">AVERAGE(D5:D8)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="16" t="n">
         <f aca="false">AVERAGE(E5:E8)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="16" t="n">
         <f aca="false">AVERAGE(F5:F8)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="16" t="n">
         <f aca="false">AVERAGE(G5:G8)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="15" t="n">
+      <c r="H9" s="16" t="n">
         <f aca="false">AVERAGE(H5:H8)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="15" t="n">
+      <c r="I9" s="16" t="n">
         <f aca="false">AVERAGE(I5:I8)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="15" t="n">
+      <c r="J9" s="16" t="n">
         <f aca="false">AVERAGE(J5:J8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <f aca="false">SUM(C9:J9)</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1169,106 +1173,106 @@
   <dimension ref="B2:D15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="44"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="10" t="n">
         <f aca="false">C5*C6/10000</f>
         <v>0</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="14" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="10" t="n">
         <f aca="false">C7*C8</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="11" t="n">
         <f aca="false">C12+C13+C9</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="18" t="str">
+      <c r="C15" s="19" t="str">
         <f aca="false">IFERROR(C14/'Unit Economics'!C16,"-")</f>
         <v>-</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="14" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1291,104 +1295,104 @@
   <dimension ref="B2:F14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="20" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/23_Fintech_Payments/_template_FINTECH.xlsx
+++ b/23_Fintech_Payments/_template_FINTECH.xlsx
@@ -10,9 +10,12 @@
   <sheets>
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Unit Economics" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Cohort Retention" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Fraud &amp; Risk" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="RefreshLog" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Interchange Economics" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Cohort Retention" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Fraud &amp; Risk" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Sources" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Checks" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="RefreshLog" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="112">
   <si>
     <t xml:space="preserve">[COMPANY] — Fintech / Payments Model</t>
   </si>
@@ -107,6 +110,57 @@
     <t xml:space="preserve">CAC payback period (months)</t>
   </si>
   <si>
+    <t xml:space="preserve">Interchange Economics — Durbin-Regulated vs. Exempt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reg II caps DEBIT interchange for issuers with &gt;$10B in assets. Issuers below that threshold are EXEMPT and can charge network-published unregulated rates -- roughly 3x higher on typical transaction sizes. This is the actual structural reason many neobanks partner with a small "sponsor bank" rather than becoming a bank themselves: it isn't just charter overhead, it's interchange economics.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average transaction size ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPV this period ($/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimated transaction count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulated (Durbin-capped, issuing bank &gt; $10B assets)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interchange per transaction (Reg II cap: $0.22 + 0.05% x txn size)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective interchange rate (% of TPV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interchange income/cost this period (rate x TPV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exempt (Durbin-exempt, issuing bank &lt; $10B assets -- typical sponsor-bank structure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interchange per transaction (network unregulated rate: $0.04 + 1.65% x txn size)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exempt vs. Regulated Advantage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$ difference this period (exempt - regulated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annualized $ difference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exempt uplift (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is a per-transaction-size-dependent advantage -- it shrinks toward zero as average ticket size grows, since the ad-valorem component matters more than the fixed component at high ticket sizes.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cohort Retention (% of cohort still active)</t>
   </si>
   <si>
@@ -164,9 +218,6 @@
     <t xml:space="preserve">Fraud, Chargeback &amp; Credit Loss</t>
   </si>
   <si>
-    <t xml:space="preserve">Inputs</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fraud loss rate (bps of TPV)</t>
   </si>
   <si>
@@ -195,6 +246,105 @@
   </si>
   <si>
     <t xml:space="preserve">Card networks typically flag issuers/acquirers above ~90-100bps fraud-to-TPV as a monitoring risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What each material assumption or convention in this model comes from.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption / convention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reg II regulated debit interchange cap ($0.22 + 0.05%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Reserve Regulation II (Durbin Amendment implementing rule), covered issuers &gt;$10B in assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statutory/regulatory cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Includes the optional $0.01 fraud-prevention adjustment folded into the $0.22 base; actual issuer cap can vary slightly by fraud-prevention-standard compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durbin-exempt unregulated debit rate ($0.04 + 1.65%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network-published unregulated debit interchange schedules (Visa/Mastercard), issuers &lt;$10B in assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard practice / network schedules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Illustrative approximation of published schedules -- actual rates vary by card program, merchant category, and network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LTV = monthly revenue x gross margin x customer lifetime (1/churn)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard SaaS/subscription LTV formula adapted for fintech unit economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumes constant monthly churn -- the Cohort Retention tab's curve-implied multiplier is the more honest number when churn is front-loaded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraud loss rate in bps of TPV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard payments-industry convention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Card networks typically flag issuers/acquirers above ~90-100bps fraud-to-TPV as a monitoring risk, per the Fraud &amp; Risk tab's note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live reconciliation identities -- independent of the model's own formulas, must tie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passes when</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exempt interchange income exceeds regulated at typical ticket sizes ($40 test)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE at the $40 default -- confirms the Durbin-exempt advantage is actually wired, not just labeled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interchange income ties: rate x TPV = per-txn fee x transaction count (Regulated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (exact) once TPV is populated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interchange income ties: rate x TPV = per-txn fee x transaction count (Exempt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cohort M0 retention is always 100% by definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
@@ -219,17 +369,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.00%;\(0.00%\);\-"/>
     <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.00\x"/>
-    <numFmt numFmtId="170" formatCode="0.00"/>
+    <numFmt numFmtId="170" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="171" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="172" formatCode="0.00"/>
+    <numFmt numFmtId="173" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,6 +436,13 @@
       <i val="true"/>
       <sz val="8"/>
       <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -372,7 +531,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -433,6 +592,30 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="170" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -441,7 +624,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -453,8 +636,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -940,12 +1135,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:J12"/>
+  <dimension ref="B2:D23"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -953,205 +1149,139 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="9" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="9" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="9" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="C6" s="15" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="C7" s="16" t="n">
+        <f aca="false">'Unit Economics'!C5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="C8" s="17" t="n">
+        <f aca="false">IFERROR(C7/C6,"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="9" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="C11" s="18" t="n">
+        <f aca="false">0.22+0.0005*C6</f>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="C12" s="19" t="n">
+        <f aca="false">IFERROR(C11/C6,"-")</f>
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+      <c r="C13" s="11" t="n">
+        <f aca="false">IFERROR(C12*C7,"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="s">
+      <c r="C16" s="18" t="n">
+        <f aca="false">0.04+0.0165*C6</f>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="19" t="n">
+        <f aca="false">IFERROR(C16/C6,"-")</f>
+        <v>0.0175</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <f aca="false">IFERROR(C17*C7,"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="3" t="s">
+      <c r="C21" s="11" t="n">
+        <f aca="false">C18-C13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="16" t="n">
-        <f aca="false">AVERAGE(C5:C8)</f>
-        <v>1</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <f aca="false">AVERAGE(D5:D8)</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <f aca="false">AVERAGE(E5:E8)</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <f aca="false">AVERAGE(F5:F8)</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <f aca="false">AVERAGE(G5:G8)</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="16" t="n">
-        <f aca="false">AVERAGE(H5:H8)</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="16" t="n">
-        <f aca="false">AVERAGE(I5:I8)</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="16" t="n">
-        <f aca="false">AVERAGE(J5:J8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+      <c r="C22" s="10" t="n">
+        <f aca="false">C21*12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="17" t="n">
-        <f aca="false">SUM(C9:J9)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="14" t="s">
+      <c r="C23" s="20" t="str">
+        <f aca="false">IFERROR(C18/C13-1,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D23" s="14" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="14" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1170,110 +1300,218 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:D15"/>
+  <dimension ref="B2:J12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>46</v>
       </c>
+      <c r="D4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="6" t="n">
+      <c r="B5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="18" t="n">
-        <v>8</v>
+      <c r="B6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="18" t="n">
+      <c r="B7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>25</v>
+      <c r="B8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>0</v>
+      <c r="B9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="22" t="n">
+        <f aca="false">AVERAGE(C5:C8)</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="22" t="n">
+        <f aca="false">AVERAGE(D5:D8)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="22" t="n">
+        <f aca="false">AVERAGE(E5:E8)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <f aca="false">AVERAGE(F5:F8)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <f aca="false">AVERAGE(G5:G8)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="22" t="n">
+        <f aca="false">AVERAGE(H5:H8)</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="22" t="n">
+        <f aca="false">AVERAGE(I5:I8)</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="22" t="n">
+        <f aca="false">AVERAGE(J5:J8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="23" t="n">
+        <f aca="false">SUM(C9:J9)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>18</v>
+      <c r="B11" s="14" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="10" t="n">
-        <f aca="false">C5*C6/10000</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="10" t="n">
-        <f aca="false">C7*C8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="11" t="n">
-        <f aca="false">C12+C13+C9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="19" t="str">
-        <f aca="false">IFERROR(C14/'Unit Economics'!C16,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>56</v>
+      <c r="B12" s="14" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1292,6 +1530,328 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:D15"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="44"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="24" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <f aca="false">C5*C6/10000</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <f aca="false">C7*C8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <f aca="false">C12+C13+C9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="25" t="str">
+        <f aca="false">IFERROR(C14/'Unit Economics'!C16,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:E9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:D9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="29" t="b">
+        <f aca="false">IF('Interchange Economics'!C6=40,'Interchange Economics'!C18&gt;'Interchange Economics'!C13,TRUE())</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="29" t="n">
+        <f aca="false">IFERROR('Interchange Economics'!C13-('Interchange Economics'!C11*'Interchange Economics'!C8),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="29" t="n">
+        <f aca="false">IFERROR('Interchange Economics'!C18-('Interchange Economics'!C16*'Interchange Economics'!C8),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="29" t="b">
+        <f aca="false">IF(COUNTIF('Cohort Retention'!C5:C8,1)=4,TRUE(),FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:F14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1304,95 +1864,95 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>62</v>
+      <c r="B4" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
